--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,8 +779,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134827131</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134827131</v>
+        <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>99853</v>
+        <v>98196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222306</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärnstarr</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex echinata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Murray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storagen, Vrm</t>
+          <t>Kråknäbben sydväst, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449568</v>
+        <v>449599</v>
       </c>
       <c r="R2" t="n">
-        <v>6665304</v>
+        <v>6665278</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ytterslänt nära lupinbestånd. Sydvästra sidan vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,24 +779,1189 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440295</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134827131</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99853</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>449568</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6665304</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Caroline Ahlgren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Caroline Ahlgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134827131</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136440360</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kråknäbben sydväst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>449569</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6665305</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 50 ex spritt på 10 meter med punkt som centrummått. Förekommer i hela vägområdet</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440360</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136440361</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kråknäbben sydväst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>449559</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665312</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 60 plantor, majoriteten i innerslänt men förekommer även i ytterslänt och dikesbotten. Spritt på ca 8 meter med punkt som centrummått</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440361</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136440362</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kråknäbben sydväst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>449553</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6665321</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex inom 7 meter, ytterslänt. Punkt som centrummått</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440362</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136440364</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kråknäbben, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>449534</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6665336</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>18 stänglar i ytterslänt på sydvästra sidan vägen. Spritt från punkten och ca 5 m åt vardera håll</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440364</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136440365</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kråknäbben sydväst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>449549</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6665326</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>16 plantor inom 5 meter, punkt som centrummått. Ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440365</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136440369</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kråknäbben, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>449505</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6665357</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10 stänglar i ytterslänt och 1 i innerslänt på sydvästra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440369</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136440370</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kråknäbben, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>449494</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665367</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>14 stänglar i ytterslänt på sydvästra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440370</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136440372</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kråknäbben, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>449479</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6665381</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>7 stänglar, 5 i ytterslänt och 2 i innerslänt, på sydvästra sidan vägen.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440372</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136440375</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99248</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kråknäbben, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>449462</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6665407</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 stänglar, en i ytterslänt och en i innerslänt, på sydvästra sidan vägen.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136440375</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28915-2026 artfynd.xlsx
+++ b/artfynd/A 28915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440295</v>
       </c>
       <c r="B2" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136440360</v>
       </c>
       <c r="B4" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136440361</v>
       </c>
       <c r="B5" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>136440362</v>
       </c>
       <c r="B6" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136440364</v>
       </c>
       <c r="B7" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136440365</v>
       </c>
       <c r="B8" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>136440369</v>
       </c>
       <c r="B9" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>136440370</v>
       </c>
       <c r="B10" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>136440372</v>
       </c>
       <c r="B11" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>136440375</v>
       </c>
       <c r="B12" t="n">
-        <v>99261</v>
+        <v>99262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
